--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-category.xlsx
+++ b/docs/CodeSystem-data-category.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="60">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>9</t>
   </si>
   <si>
     <t>Level</t>
@@ -169,6 +169,18 @@
   </si>
   <si>
     <t>Proteomics</t>
+  </si>
+  <si>
+    <t>epigenomics</t>
+  </si>
+  <si>
+    <t>Epigenomics</t>
+  </si>
+  <si>
+    <t>multi-omic</t>
+  </si>
+  <si>
+    <t>Multi-omic</t>
   </si>
   <si>
     <t>metabolomics</t>
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -591,6 +603,30 @@
       </c>
       <c r="D8" s="2"/>
     </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
